--- a/data/metric_types.xlsx
+++ b/data/metric_types.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/WearingPositionError_2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDDAEDE-AE1F-4B40-937F-E8CBF81225F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399BCB6B-CB57-6742-8871-5E2ADCD42142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="29460" windowWidth="28240" windowHeight="21680" xr2:uid="{C7CE30F9-32C8-3B48-9C95-A21A5EBA7D2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="91">
   <si>
     <t>name</t>
   </si>
@@ -131,16 +131,10 @@
     <t>engine</t>
   </si>
   <si>
-    <t>Mean (log) mel EDI</t>
-  </si>
-  <si>
     <t>Duration crossing threshold</t>
   </si>
   <si>
     <t>Timing crossing threshold</t>
-  </si>
-  <si>
-    <t>Brightest/Darkest period</t>
   </si>
   <si>
     <t>lmer</t>
@@ -309,6 +303,12 @@
   </si>
   <si>
     <t>+ (position|Id) + (1|Date)</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>Brightest / Darkest period</t>
   </si>
 </sst>
 </file>
@@ -14023,6 +14023,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="35.5" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="5" max="5" width="25.6640625" customWidth="1"/>
     <col min="8" max="8" width="24.33203125" customWidth="1"/>
   </cols>
@@ -14041,16 +14042,16 @@
         <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -14061,17 +14062,17 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -14082,38 +14083,40 @@
         <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -14121,22 +14124,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -14144,20 +14147,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -14165,20 +14168,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -14186,20 +14189,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -14207,22 +14210,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -14230,20 +14233,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -14251,20 +14254,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -14272,20 +14275,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -14293,20 +14296,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -14314,62 +14317,62 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -14377,353 +14380,353 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -14731,20 +14734,20 @@
         <v>15</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -14752,20 +14755,20 @@
         <v>16</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -14773,146 +14776,146 @@
         <v>17</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -14926,14 +14929,14 @@
         <v>23</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -14947,260 +14950,260 @@
         <v>24</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/metric_types.xlsx
+++ b/data/metric_types.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/WearingPositionError_2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399BCB6B-CB57-6742-8871-5E2ADCD42142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70B0030-8B90-7246-9653-6DD39612B29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="29460" windowWidth="28240" windowHeight="21680" xr2:uid="{C7CE30F9-32C8-3B48-9C95-A21A5EBA7D2B}"/>
+    <workbookView xWindow="6380" yWindow="780" windowWidth="34740" windowHeight="25800" xr2:uid="{C7CE30F9-32C8-3B48-9C95-A21A5EBA7D2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -13699,6 +13699,358 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1205" name="AutoShape 18">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{221D4B2E-5928-DF40-B944-7FB7F43FFA3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8534400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1206" name="AutoShape 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11A48C70-F949-D94B-97B2-3E20EB2AA3F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1207" name="AutoShape 20">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D8F7E8A-8F48-7E49-914E-609E559D1D6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1208" name="AutoShape 21">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE19C566-5AC4-5046-88ED-60FEBB1C9FE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1209" name="AutoShape 18">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D43DE8A1-342E-EF4D-A0C5-71B82A612A56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8534400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1210" name="AutoShape 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{879CB121-E30C-AC40-AB6B-8D3487334552}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1262" name="AutoShape 20">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D60DCC-B6C1-DC43-9E2A-6215BCBE8543}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1263" name="AutoShape 21">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F308303-BF6C-7940-9C29-B5591C0FCD52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6731000" y="8737600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -14428,7 +14780,7 @@
         <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
@@ -14452,7 +14804,7 @@
         <v>43</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
@@ -14971,7 +15323,7 @@
         <v>43</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>36</v>
